--- a/Tools/Config/Datas/AbilitySetting.xlsx
+++ b/Tools/Config/Datas/AbilitySetting.xlsx
@@ -2302,40 +2302,40 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="0" t="n">
         <v>14001</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>谐度破坏</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>ActiveSkill</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="G19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="0" t="n">
         <v>14001</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T19" s="0" t="inlineStr">
         <is>
           <t>HarmonyBreak</t>
         </is>
       </c>
-      <c r="U19" t="n">
+      <c r="U19" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col width="16.4545454545455" customWidth="1" style="2" min="3" max="3"/>
@@ -2968,6 +2968,11 @@
           <t>DazeRatio</t>
         </is>
       </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>VibrationRatio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2984,6 +2989,7 @@
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="8" t="n"/>
       <c r="L2" s="8" t="n"/>
+      <c r="M2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -3046,6 +3052,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3106,6 +3117,11 @@
       <c r="L4" s="4" t="inlineStr">
         <is>
           <t>失衡倍率</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>共振度倍率</t>
         </is>
       </c>
     </row>
@@ -3160,6 +3176,11 @@
       <c r="L5" s="11" t="inlineStr">
         <is>
           <t>0=不贡献。积蓄=100*本值*(1-抗性)。杂兵上限100时 0.55=两下11001满</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>0=本段不削韧；破坏技填 0，走 VibrationRule.TuneBreakVibrationPct</t>
         </is>
       </c>
     </row>
@@ -3203,6 +3224,9 @@
       <c r="L6" s="0" t="n">
         <v>0.55</v>
       </c>
+      <c r="M6" s="0" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n"/>
@@ -3244,6 +3268,9 @@
       <c r="L7" s="0" t="n">
         <v>0.35</v>
       </c>
+      <c r="M7" s="0" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
@@ -3285,6 +3312,9 @@
       <c r="L8" s="0" t="n">
         <v>0.35</v>
       </c>
+      <c r="M8" s="0" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="n">
@@ -3325,6 +3355,9 @@
       <c r="L9" s="0" t="n">
         <v>0.9</v>
       </c>
+      <c r="M9" s="0" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="n">
@@ -3365,6 +3398,9 @@
       <c r="L10" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M10" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="n">
@@ -3405,6 +3441,9 @@
       <c r="L11" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M11" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
@@ -3445,6 +3484,9 @@
       <c r="L12" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M12" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
@@ -3485,6 +3527,9 @@
       <c r="L13" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M13" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
@@ -3525,6 +3570,9 @@
       <c r="L14" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M14" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
@@ -3565,6 +3613,9 @@
       <c r="L15" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M15" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="n">
@@ -3605,6 +3656,9 @@
       <c r="L16" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M16" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="n">
@@ -3645,6 +3699,9 @@
       <c r="L17" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M17" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="n">
@@ -3685,6 +3742,9 @@
       <c r="L18" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M18" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="n">
@@ -3725,6 +3785,9 @@
       <c r="L19" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M19" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
@@ -3765,204 +3828,222 @@
       <c r="L20" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="M20" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>14001</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>谐度破坏</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="G21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>14001</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>谐度破坏</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="G22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>14001</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>谐度破坏</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="G23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="0" t="n">
         <v>14001</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>谐度破坏</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="G24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="0" t="n">
         <v>14001</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>谐度破坏</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>5|5.5|6|6.5|7|7.5|8|8.5|9|9.5</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>Physic</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="G25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="0" t="n">
         <v>0</v>
       </c>
     </row>
